--- a/artfynd/A 28430-2025 artfynd.xlsx
+++ b/artfynd/A 28430-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83884401</v>
+        <v>83885029</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>743460.7909396385</v>
+        <v>743410</v>
       </c>
       <c r="R2" t="n">
-        <v>7068595.105438618</v>
+        <v>7068618</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -751,19 +746,9 @@
           <t>2020-03-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-03-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,22 +769,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Roger Olofsson, Anders Hällström, Linnea Helmersson</t>
+          <t>Roger Olofsson, Linnea Helmersson, Anders Hällström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>83885068</v>
+        <v>83885048</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>743407.1342139154</v>
+        <v>743492</v>
       </c>
       <c r="R3" t="n">
-        <v>7068607.903907268</v>
+        <v>7068603</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -867,19 +847,9 @@
           <t>2020-03-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-03-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>83884663</v>
+        <v>83885059</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>743495.1652515247</v>
+        <v>743495</v>
       </c>
       <c r="R4" t="n">
-        <v>7068571.904186627</v>
+        <v>7068556</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -983,19 +948,9 @@
           <t>2020-03-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-03-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>83884542</v>
+        <v>83885068</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>743455.8633489769</v>
+        <v>743407</v>
       </c>
       <c r="R5" t="n">
-        <v>7068682.092725129</v>
+        <v>7068608</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1099,19 +1049,9 @@
           <t>2020-03-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-03-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>83885029</v>
+        <v>112997360</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,22 +1108,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ysseltjärn, Vb</t>
+          <t>Ysseltjärnen, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>743409.9317013039</v>
+        <v>743448</v>
       </c>
       <c r="R6" t="n">
-        <v>7068617.926362654</v>
+        <v>7068599</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,22 +1144,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-03-14</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-03-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,34 +1158,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Roger Olofsson, Linnea Helmersson, Anders Hällström</t>
+          <t>Joakim Karlsson, Isac Printz, Linnea Andersson, Jörgen Nilsson, Tommy Magnusson, maria boekraad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>83885059</v>
+        <v>112997366</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,40 +1187,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ysseltjärn, Vb</t>
+          <t>Ysseltjärnen, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>743495.0653459878</v>
+        <v>743430</v>
       </c>
       <c r="R7" t="n">
-        <v>7068555.848967532</v>
+        <v>7068614</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,22 +1241,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-03-14</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-03-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,56 +1255,50 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Roger Olofsson, Linnea Helmersson, Anders Hällström</t>
+          <t>Joakim Karlsson, Isac Printz, Linnea Andersson, Jörgen Nilsson, Tommy Magnusson, maria boekraad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>83884591</v>
+        <v>83884401</v>
       </c>
       <c r="B8" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1414,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>743440.0018294054</v>
+        <v>743461</v>
       </c>
       <c r="R8" t="n">
-        <v>7068615.789041151</v>
+        <v>7068595</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1447,19 +1344,9 @@
           <t>2020-03-14</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-03-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,63 +1367,55 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Roger Olofsson, Linnea Helmersson, Anders Hällström</t>
+          <t>Roger Olofsson, Anders Hällström, Linnea Helmersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>83884626</v>
+        <v>83893679</v>
       </c>
       <c r="B9" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ysseltjärn, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>743465.910252679</v>
+        <v>743451</v>
       </c>
       <c r="R9" t="n">
-        <v>7068598.175059724</v>
+        <v>7068622</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1560,22 +1439,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-03-14</t>
+          <t>2020-03-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-03-14</t>
+          <t>2020-03-26</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,38 +1463,52 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Roger Olofsson, Linnea Helmersson, Anders Hällström</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>83884567</v>
+        <v>83884542</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1646,10 +1539,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>743509.0013456258</v>
+        <v>743456</v>
       </c>
       <c r="R10" t="n">
-        <v>7068704.915299426</v>
+        <v>7068682</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1679,19 +1572,9 @@
           <t>2020-03-14</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-03-14</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,37 +1602,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>83885048</v>
+        <v>83884567</v>
       </c>
       <c r="B11" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1762,10 +1640,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>743491.8837833119</v>
+        <v>743509</v>
       </c>
       <c r="R11" t="n">
-        <v>7068602.854175337</v>
+        <v>7068705</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1795,19 +1673,9 @@
           <t>2020-03-14</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-03-14</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,61 +1703,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>83884993</v>
+        <v>83893672</v>
       </c>
       <c r="B12" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ysseltjärn, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>743453.1453199527</v>
+        <v>743450</v>
       </c>
       <c r="R12" t="n">
-        <v>7068595.852701938</v>
+        <v>7068701</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1913,22 +1768,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2020-03-14</t>
+          <t>2020-03-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2020-03-14</t>
+          <t>2020-03-26</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1939,77 +1794,84 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Roger Olofsson, Linnea Helmersson, Anders Hällström</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>83885001</v>
+        <v>83893673</v>
       </c>
       <c r="B13" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ysseltjärn, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>743513.147505415</v>
+        <v>743452</v>
       </c>
       <c r="R13" t="n">
-        <v>7068604.941169376</v>
+        <v>7068660</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2033,22 +1895,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2020-03-14</t>
+          <t>2020-03-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2020-03-14</t>
+          <t>2020-03-26</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,35 +1921,50 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Roger Olofsson, Linnea Helmersson, Anders Hällström</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>83893673</v>
+        <v>83893674</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2115,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>743452.2145569783</v>
+        <v>743535</v>
       </c>
       <c r="R14" t="n">
-        <v>7068659.969478985</v>
+        <v>7068791</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2179,17 +2056,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2207,37 +2084,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>83893679</v>
+        <v>83893675</v>
       </c>
       <c r="B15" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2247,10 +2119,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>743451.1278174709</v>
+        <v>743487</v>
       </c>
       <c r="R15" t="n">
-        <v>7068621.996665574</v>
+        <v>7068715</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2339,37 +2211,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>83893677</v>
+        <v>83893676</v>
       </c>
       <c r="B16" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2379,10 +2246,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>743429.0451846214</v>
+        <v>743482</v>
       </c>
       <c r="R16" t="n">
-        <v>7068618.955383505</v>
+        <v>7068701</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2471,53 +2338,56 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>83893676</v>
+        <v>83884993</v>
       </c>
       <c r="B17" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ysseltjärn, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>743482.072890588</v>
+        <v>743453</v>
       </c>
       <c r="R17" t="n">
-        <v>7068701.053832136</v>
+        <v>7068596</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2541,22 +2411,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2020-03-26</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2020-03-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2020-03-26</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2020-03-14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2567,89 +2427,72 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Roger Olofsson, Linnea Helmersson, Anders Hällström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>83893672</v>
+        <v>83885001</v>
       </c>
       <c r="B18" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ysseltjärn, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>743449.956008647</v>
+        <v>743513</v>
       </c>
       <c r="R18" t="n">
-        <v>7068700.803896544</v>
+        <v>7068605</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2673,22 +2516,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2020-03-26</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2020-03-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2020-03-26</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2020-03-14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2699,51 +2532,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Roger Olofsson, Linnea Helmersson, Anders Hällström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>83893675</v>
+        <v>83885020</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2751,37 +2559,45 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ysseltjärn, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>743486.8148946085</v>
+        <v>743509</v>
       </c>
       <c r="R19" t="n">
-        <v>7068714.792145951</v>
+        <v>7068573</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2805,22 +2621,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2020-03-26</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2020-03-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2020-03-26</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2020-03-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2831,51 +2637,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Roger Olofsson, Linnea Helmersson, Anders Hällström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112997369</v>
+        <v>83893671</v>
       </c>
       <c r="B20" t="n">
-        <v>90047</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2883,37 +2664,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ysseltjärnen, Vb</t>
+          <t>Ysseltjärn, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>743451</v>
+        <v>743446</v>
       </c>
       <c r="R20" t="n">
-        <v>7068640</v>
+        <v>7068710</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2937,12 +2727,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2020-03-26</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2020-03-26</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2953,223 +2753,39 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joakim Karlsson, Isac Printz, Linnea Andersson, Jörgen Nilsson, Tommy Magnusson, maria boekraad</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>112997360</v>
-      </c>
-      <c r="B21" t="n">
-        <v>90029</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Ysseltjärnen, Vb</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>743448</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7068599</v>
-      </c>
-      <c r="S21" t="n">
-        <v>15</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Hörnefors</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Joakim Karlsson, Isac Printz, Linnea Andersson, Jörgen Nilsson, Tommy Magnusson, maria boekraad</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>112997366</v>
-      </c>
-      <c r="B22" t="n">
-        <v>90469</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Ysseltjärnen, Vb</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>743431</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7068614</v>
-      </c>
-      <c r="S22" t="n">
-        <v>15</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Hörnefors</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Joakim Karlsson, Isac Printz, Linnea Andersson, Jörgen Nilsson, Tommy Magnusson, maria boekraad</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28430-2025 artfynd.xlsx
+++ b/artfynd/A 28430-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83885029</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83885048</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83885059</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83885068</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112997360</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1270,6 +1300,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112997366</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83884401</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1498,6 +1538,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83893679</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1599,6 +1644,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83884542</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1700,6 +1750,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83884567</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1827,6 +1882,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83893672</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1954,6 +2014,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83893673</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2081,6 +2146,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83893674</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2208,6 +2278,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83893675</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2335,6 +2410,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83893676</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2440,6 +2520,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83884993</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2545,6 +2630,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83885001</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2650,6 +2740,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83885020</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2786,8 +2881,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83893671</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>